--- a/demo_migrations/migration-tests.xlsx
+++ b/demo_migrations/migration-tests.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ashley.wong/fpl-ccd-configuration/demo_migrations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDCFC263-9D22-B645-9EE0-5223D4EF09C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E65E1543-764B-164E-926D-27585A5C3229}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3760" yWindow="2060" windowWidth="28040" windowHeight="17440" xr2:uid="{736675D8-260A-3245-8C1F-3273721D880A}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="35">
   <si>
     <t>demo</t>
   </si>
@@ -129,6 +129,18 @@
   </si>
   <si>
     <t>CORRESPODNDENCE</t>
+  </si>
+  <si>
+    <t>Any Other Document (relates to hearing) - Child Guardian Reports</t>
+  </si>
+  <si>
+    <t>Any Other Document (relates to hearing) - Applicant Statement</t>
+  </si>
+  <si>
+    <t>Any Other Document (non-hearing) - Applicant Statement</t>
+  </si>
+  <si>
+    <t>Any Other Document (non-hearing) - Expert Reports - Phsychiatric</t>
   </si>
 </sst>
 </file>
@@ -482,12 +494,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21860505-AE12-0F49-A9FE-8EF91D5404DC}">
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="17.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.33203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="28" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="56.33203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10" bestFit="1" customWidth="1"/>
   </cols>
@@ -728,10 +740,10 @@
     </row>
     <row r="19" spans="4:6" x14ac:dyDescent="0.2">
       <c r="D19" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="E19" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="F19" t="s">
         <v>12</v>
@@ -739,10 +751,10 @@
     </row>
     <row r="20" spans="4:6" x14ac:dyDescent="0.2">
       <c r="D20" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E20" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F20" t="s">
         <v>12</v>
@@ -750,10 +762,10 @@
     </row>
     <row r="21" spans="4:6" x14ac:dyDescent="0.2">
       <c r="D21" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E21" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="F21" t="s">
         <v>12</v>
@@ -761,10 +773,10 @@
     </row>
     <row r="22" spans="4:6" x14ac:dyDescent="0.2">
       <c r="D22" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E22" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F22" t="s">
         <v>12</v>
@@ -772,10 +784,10 @@
     </row>
     <row r="23" spans="4:6" x14ac:dyDescent="0.2">
       <c r="D23" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E23" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="F23" t="s">
         <v>12</v>
@@ -783,10 +795,10 @@
     </row>
     <row r="24" spans="4:6" x14ac:dyDescent="0.2">
       <c r="D24" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E24" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="F24" t="s">
         <v>12</v>
@@ -794,10 +806,10 @@
     </row>
     <row r="25" spans="4:6" x14ac:dyDescent="0.2">
       <c r="D25" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E25" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="F25" t="s">
         <v>12</v>
@@ -805,23 +817,111 @@
     </row>
     <row r="26" spans="4:6" x14ac:dyDescent="0.2">
       <c r="D26" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E26" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="F26" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="27" spans="4:6" x14ac:dyDescent="0.2">
       <c r="D27" t="s">
+        <v>25</v>
+      </c>
+      <c r="E27" t="s">
+        <v>24</v>
+      </c>
+      <c r="F27" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28" spans="4:6" x14ac:dyDescent="0.2">
+      <c r="D28" t="s">
+        <v>26</v>
+      </c>
+      <c r="E28" t="s">
+        <v>24</v>
+      </c>
+      <c r="F28" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="29" spans="4:6" x14ac:dyDescent="0.2">
+      <c r="D29" t="s">
+        <v>27</v>
+      </c>
+      <c r="E29" t="s">
+        <v>24</v>
+      </c>
+      <c r="F29" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30" spans="4:6" x14ac:dyDescent="0.2">
+      <c r="D30" t="s">
+        <v>28</v>
+      </c>
+      <c r="E30" t="s">
+        <v>24</v>
+      </c>
+      <c r="F30" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31" spans="4:6" x14ac:dyDescent="0.2">
+      <c r="D31" t="s">
+        <v>29</v>
+      </c>
+      <c r="E31" t="s">
+        <v>24</v>
+      </c>
+      <c r="F31" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="32" spans="4:6" x14ac:dyDescent="0.2">
+      <c r="D32" t="s">
         <v>30</v>
       </c>
-      <c r="E27" t="s">
-        <v>14</v>
-      </c>
-      <c r="F27" t="s">
+      <c r="E32" t="s">
+        <v>2</v>
+      </c>
+      <c r="F32" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="33" spans="4:6" x14ac:dyDescent="0.2">
+      <c r="D33" t="s">
+        <v>30</v>
+      </c>
+      <c r="E33" t="s">
+        <v>14</v>
+      </c>
+      <c r="F33" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34" spans="4:6" x14ac:dyDescent="0.2">
+      <c r="D34" t="s">
+        <v>30</v>
+      </c>
+      <c r="E34" t="s">
+        <v>2</v>
+      </c>
+      <c r="F34" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="4:6" x14ac:dyDescent="0.2">
+      <c r="D35" t="s">
+        <v>30</v>
+      </c>
+      <c r="E35" t="s">
+        <v>14</v>
+      </c>
+      <c r="F35" t="s">
         <v>3</v>
       </c>
     </row>

--- a/demo_migrations/migration-tests.xlsx
+++ b/demo_migrations/migration-tests.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ashley.wong/fpl-ccd-configuration/demo_migrations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E65E1543-764B-164E-926D-27585A5C3229}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB6E1C1F-5225-2D47-84E6-B2EC8F7D4757}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3760" yWindow="2060" windowWidth="28040" windowHeight="17440" xr2:uid="{736675D8-260A-3245-8C1F-3273721D880A}"/>
+    <workbookView xWindow="12800" yWindow="540" windowWidth="23040" windowHeight="19920" xr2:uid="{736675D8-260A-3245-8C1F-3273721D880A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="35">
   <si>
     <t>demo</t>
   </si>
@@ -147,7 +147,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -155,13 +155,25 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF9C5700"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -173,15 +185,20 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1"/>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="1" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Neutral" xfId="1" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -555,373 +572,439 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
+    <row r="4" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E4" t="s">
-        <v>2</v>
-      </c>
-      <c r="F4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="D5" t="s">
+      <c r="E4" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E5" t="s">
-        <v>2</v>
-      </c>
-      <c r="F5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="D6" t="s">
+      <c r="E5" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="D7" t="s">
+      <c r="E6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
+      <c r="E7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E8" t="s">
-        <v>2</v>
-      </c>
-      <c r="F8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="D9" t="s">
+      <c r="E8" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E9" t="s">
-        <v>14</v>
-      </c>
-      <c r="F9" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="D10" t="s">
+      <c r="E9" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="E10" t="s">
-        <v>2</v>
-      </c>
-      <c r="F10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="D11" t="s">
+      <c r="E10" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="E11" t="s">
-        <v>14</v>
-      </c>
-      <c r="F11" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="D12" t="s">
+      <c r="E11" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E12" t="s">
-        <v>2</v>
-      </c>
-      <c r="F12" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="D13" t="s">
+      <c r="E12" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E13" t="s">
-        <v>14</v>
-      </c>
-      <c r="F13" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="D14" t="s">
+      <c r="E13" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E14" t="s">
-        <v>2</v>
-      </c>
-      <c r="F14" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="D15" t="s">
+      <c r="E14" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E15" t="s">
-        <v>14</v>
-      </c>
-      <c r="F15" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="D16" t="s">
+      <c r="E15" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E16" t="s">
-        <v>14</v>
-      </c>
-      <c r="F16" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="17" spans="4:6" x14ac:dyDescent="0.2">
-      <c r="D17" t="s">
+      <c r="E16" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F17" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" spans="4:6" x14ac:dyDescent="0.2">
-      <c r="D18" t="s">
+      <c r="E17" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E18" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F18" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="19" spans="4:6" x14ac:dyDescent="0.2">
-      <c r="D19" t="s">
+      <c r="F18" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E19" t="s">
-        <v>2</v>
-      </c>
-      <c r="F19" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="20" spans="4:6" x14ac:dyDescent="0.2">
-      <c r="D20" t="s">
+      <c r="E19" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E20" t="s">
-        <v>14</v>
-      </c>
-      <c r="F20" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="21" spans="4:6" x14ac:dyDescent="0.2">
-      <c r="D21" t="s">
+      <c r="E20" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="2:6" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E21" t="s">
-        <v>2</v>
-      </c>
-      <c r="F21" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="22" spans="4:6" x14ac:dyDescent="0.2">
-      <c r="D22" t="s">
+      <c r="E21" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E22" t="s">
-        <v>14</v>
-      </c>
-      <c r="F22" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="23" spans="4:6" x14ac:dyDescent="0.2">
-      <c r="D23" t="s">
+      <c r="E22" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B23" s="5"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E23" t="s">
-        <v>2</v>
-      </c>
-      <c r="F23" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="24" spans="4:6" x14ac:dyDescent="0.2">
-      <c r="D24" t="s">
+      <c r="E23" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B24" s="5"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E24" t="s">
-        <v>14</v>
-      </c>
-      <c r="F24" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="25" spans="4:6" x14ac:dyDescent="0.2">
-      <c r="D25" t="s">
+      <c r="E24" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B25" s="5"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="E25" t="s">
-        <v>2</v>
-      </c>
-      <c r="F25" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="26" spans="4:6" x14ac:dyDescent="0.2">
-      <c r="D26" t="s">
+      <c r="E25" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" spans="2:6" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B26" s="5"/>
+      <c r="C26" s="5"/>
+      <c r="D26" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="E26" t="s">
-        <v>14</v>
-      </c>
-      <c r="F26" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="27" spans="4:6" x14ac:dyDescent="0.2">
-      <c r="D27" t="s">
+      <c r="E26" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B27" s="5"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E27" t="s">
+      <c r="E27" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F27" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="28" spans="4:6" x14ac:dyDescent="0.2">
-      <c r="D28" t="s">
+      <c r="F27" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28" spans="2:6" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B28" s="5"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E28" t="s">
+      <c r="E28" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F28" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="29" spans="4:6" x14ac:dyDescent="0.2">
-      <c r="D29" t="s">
+      <c r="F28" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B29" s="5"/>
+      <c r="C29" s="5"/>
+      <c r="D29" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E29" t="s">
+      <c r="E29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F29" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="30" spans="4:6" x14ac:dyDescent="0.2">
-      <c r="D30" t="s">
+      <c r="F29" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B30" s="5"/>
+      <c r="C30" s="5"/>
+      <c r="D30" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="E30" t="s">
+      <c r="E30" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F30" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="31" spans="4:6" x14ac:dyDescent="0.2">
-      <c r="D31" t="s">
+      <c r="F30" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B31" s="5"/>
+      <c r="C31" s="5"/>
+      <c r="D31" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E31" t="s">
+      <c r="E31" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F31" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="32" spans="4:6" x14ac:dyDescent="0.2">
-      <c r="D32" t="s">
+      <c r="F31" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B32" s="5"/>
+      <c r="C32" s="5"/>
+      <c r="D32" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E32" t="s">
-        <v>2</v>
-      </c>
-      <c r="F32" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="33" spans="4:6" x14ac:dyDescent="0.2">
-      <c r="D33" t="s">
+      <c r="E32" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="33" spans="2:6" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B33" s="5"/>
+      <c r="C33" s="5"/>
+      <c r="D33" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E33" t="s">
-        <v>14</v>
-      </c>
-      <c r="F33" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="34" spans="4:6" x14ac:dyDescent="0.2">
-      <c r="D34" t="s">
+      <c r="E33" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34" spans="2:6" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B34" s="5"/>
+      <c r="C34" s="5"/>
+      <c r="D34" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E34" t="s">
-        <v>2</v>
-      </c>
-      <c r="F34" t="s">
+      <c r="E34" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F34" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="4:6" x14ac:dyDescent="0.2">
-      <c r="D35" t="s">
+    <row r="35" spans="2:6" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B35" s="5"/>
+      <c r="C35" s="5"/>
+      <c r="D35" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E35" t="s">
-        <v>14</v>
-      </c>
-      <c r="F35" t="s">
+      <c r="E35" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F35" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/demo_migrations/migration-tests.xlsx
+++ b/demo_migrations/migration-tests.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ashley.wong/fpl-ccd-configuration/demo_migrations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB6E1C1F-5225-2D47-84E6-B2EC8F7D4757}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56C7F491-6902-814B-AB21-9EE0BD8BAD78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12800" yWindow="540" windowWidth="23040" windowHeight="19920" xr2:uid="{736675D8-260A-3245-8C1F-3273721D880A}"/>
+    <workbookView xWindow="12800" yWindow="540" windowWidth="23040" windowHeight="19920" activeTab="1" xr2:uid="{736675D8-260A-3245-8C1F-3273721D880A}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Manual" sheetId="1" r:id="rId1"/>
+    <sheet name="Auto-generated" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="42">
   <si>
     <t>demo</t>
   </si>
@@ -141,13 +142,34 @@
   </si>
   <si>
     <t>Any Other Document (non-hearing) - Expert Reports - Phsychiatric</t>
+  </si>
+  <si>
+    <t>State</t>
+  </si>
+  <si>
+    <t>kurt@swansea.gov.uk</t>
+  </si>
+  <si>
+    <t>ctsc-team-admin@justice.gov.uk</t>
+  </si>
+  <si>
+    <t>PREARING_FOR_HEARING</t>
+  </si>
+  <si>
+    <t>login user</t>
+  </si>
+  <si>
+    <t>password</t>
+  </si>
+  <si>
+    <t>Password12</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -158,6 +180,14 @@
     <font>
       <sz val="12"/>
       <color rgb="FF9C5700"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -185,19 +215,22 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="1" quotePrefix="1" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Neutral" xfId="1" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
@@ -1012,4 +1045,55 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E607EB8-8CE8-6444-A143-DE2593D0972C}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="23.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" xr:uid="{63684EDB-5B25-C445-BBB2-0B76AF7CBFE1}"/>
+    <hyperlink ref="B3" r:id="rId2" xr:uid="{A7263C5D-69B9-0743-A243-8F017832656C}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/demo_migrations/migration-tests.xlsx
+++ b/demo_migrations/migration-tests.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ashley.wong/fpl-ccd-configuration/demo_migrations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56C7F491-6902-814B-AB21-9EE0BD8BAD78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACFFF3C7-6440-1A44-9071-46A23FC7D5FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12800" yWindow="540" windowWidth="23040" windowHeight="19920" activeTab="1" xr2:uid="{736675D8-260A-3245-8C1F-3273721D880A}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="35840" windowHeight="19980" activeTab="1" xr2:uid="{736675D8-260A-3245-8C1F-3273721D880A}"/>
   </bookViews>
   <sheets>
     <sheet name="Manual" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="79">
   <si>
     <t>demo</t>
   </si>
@@ -153,9 +153,6 @@
     <t>ctsc-team-admin@justice.gov.uk</t>
   </si>
   <si>
-    <t>PREARING_FOR_HEARING</t>
-  </si>
-  <si>
     <t>login user</t>
   </si>
   <si>
@@ -163,13 +160,127 @@
   </si>
   <si>
     <t>Password12</t>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t>manageDocumentsLA</t>
+  </si>
+  <si>
+    <t>manageDocuments</t>
+  </si>
+  <si>
+    <t>solicitor1@solicitors.uk</t>
+  </si>
+  <si>
+    <t>Event Name</t>
+  </si>
+  <si>
+    <t>no. of hearings</t>
+  </si>
+  <si>
+    <t>manage-documents</t>
+  </si>
+  <si>
+    <t>manage-documents-la</t>
+  </si>
+  <si>
+    <t>manageDocumentsSolicitor</t>
+  </si>
+  <si>
+    <t>no. of respondents</t>
+  </si>
+  <si>
+    <t>1 to 2</t>
+  </si>
+  <si>
+    <t>Submitted</t>
+  </si>
+  <si>
+    <t>Callback</t>
+  </si>
+  <si>
+    <t>Document Types</t>
+  </si>
+  <si>
+    <t>@</t>
+  </si>
+  <si>
+    <t>Repeat @ for document relates to hearing</t>
+  </si>
+  <si>
+    <t>no. of child</t>
+  </si>
+  <si>
+    <t>Hearing Documents (if having hearing) &gt; Skeleton Arguments (per respondent/per child/applicant)</t>
+  </si>
+  <si>
+    <t>Hearing Documents (if having hearing) &gt; Position statement respondent (per respondent)</t>
+  </si>
+  <si>
+    <t>Hearing Documents (if having hearing) &gt; Position statement child (per child)</t>
+  </si>
+  <si>
+    <t>Hearing Documents (if having hearing) &gt; Case Summary (single case summary per hearing)</t>
+  </si>
+  <si>
+    <t>Hearing Documents (if having hearing) &gt; Court Bundle (support multiple documents, confidential: true/false)</t>
+  </si>
+  <si>
+    <t>Further documents for main application &gt; Any Other Documents (non-hearing) &gt; Other reports,  support multiple documents,  confidential: true/false)</t>
+  </si>
+  <si>
+    <t>Further documents for main application &gt; Any Other Documents (non-hearing) &gt; Expert reports &gt; (various expert report type),  support multiple documents, confidential: true/false)</t>
+  </si>
+  <si>
+    <t>Further documents for main application &gt; Any Other Documents (non-hearing) &gt; Child's guardian reports,  support multiple documents,  confidential: true/false)</t>
+  </si>
+  <si>
+    <t>Further documents for main application &gt; Any Other Documents (non-hearing) &gt; Applicant Statements,  support multiple documents, confidential: true/false)</t>
+  </si>
+  <si>
+    <t>Further documents for main application &gt; Respondent statement (per respondent, support multiple documents, confidential: true/false)</t>
+  </si>
+  <si>
+    <t>Further documents for main application &gt; Any Other Documents (non-hearing) &gt; Notice of Acting / Notice of Issue,  support multiple documents,  confidential: true/false)</t>
+  </si>
+  <si>
+    <t>Having placement and notice of placement</t>
+  </si>
+  <si>
+    <t>Y/N</t>
+  </si>
+  <si>
+    <t>Placement responses (if having placement and notice of placement) (parties: LA/Cafcass/Respondent, support multiple documents)</t>
+  </si>
+  <si>
+    <t>Further documents for main application &gt; Further application documents - for example the SWET or care plan (support multiple documents; various type of documents; confidential: true/false)</t>
+  </si>
+  <si>
+    <t>*</t>
+  </si>
+  <si>
+    <t>Repeat * for document relates to hearing</t>
+  </si>
+  <si>
+    <t>0 to N</t>
+  </si>
+  <si>
+    <t>Correspondence (support multiple documents, confidential: true/false)</t>
+  </si>
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>Repeat # for document relates to hearing</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -185,15 +296,28 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="12"/>
-      <color theme="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -205,8 +329,26 @@
         <fgColor rgb="FFFFEB9C"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -214,23 +356,58 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="1" quotePrefix="1" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="3" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="4" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="4" quotePrefix="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="3" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="4" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="3">
-    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
+  <cellStyles count="5">
+    <cellStyle name="20% - Accent1" xfId="2" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="3" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="4" builtinId="32"/>
     <cellStyle name="Neutral" xfId="1" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
@@ -794,7 +971,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="2:6" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:7" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
       <c r="D17" s="3" t="s">
@@ -807,7 +984,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="2:6" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:7" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
       <c r="D18" s="3" t="s">
@@ -820,59 +997,71 @@
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="2:6" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="5"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="3" t="s">
+    <row r="19" spans="2:7" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="E19" s="3" t="s">
+      <c r="E19" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="F19" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="20" spans="2:6" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="5"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="3" t="s">
+      <c r="F19" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B20" s="6"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="E20" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F20" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="21" spans="2:6" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="5"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="3" t="s">
+      <c r="F20" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B21" s="6"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E21" s="3" t="s">
+      <c r="E21" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="F21" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="22" spans="2:6" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="5"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="3" t="s">
+      <c r="F21" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B22" s="6"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E22" s="3" t="s">
+      <c r="E22" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="23" spans="2:6" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="F22" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
       <c r="D23" s="3" t="s">
@@ -885,7 +1074,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="24" spans="2:6" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:7" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
       <c r="D24" s="3" t="s">
@@ -898,7 +1087,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="25" spans="2:6" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:7" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
       <c r="D25" s="3" t="s">
@@ -911,7 +1100,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="26" spans="2:6" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:7" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
       <c r="D26" s="3" t="s">
@@ -924,7 +1113,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="27" spans="2:6" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:7" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
       <c r="D27" s="3" t="s">
@@ -937,7 +1126,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="28" spans="2:6" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:7" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
       <c r="D28" s="3" t="s">
@@ -950,7 +1139,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="29" spans="2:6" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:7" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
       <c r="D29" s="3" t="s">
@@ -963,7 +1152,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="30" spans="2:6" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:7" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
       <c r="D30" s="3" t="s">
@@ -976,7 +1165,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="31" spans="2:6" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:7" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B31" s="5"/>
       <c r="C31" s="5"/>
       <c r="D31" s="3" t="s">
@@ -989,7 +1178,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="32" spans="2:6" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:7" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B32" s="5"/>
       <c r="C32" s="5"/>
       <c r="D32" s="3" t="s">
@@ -1049,51 +1238,786 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E607EB8-8CE8-6444-A143-DE2593D0972C}">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:K44"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="23.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.5" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="10.83203125" style="8"/>
+    <col min="5" max="5" width="16.5" style="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="37" style="8" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="24" style="8" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.83203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="3" style="8" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="162.83203125" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A1" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C1" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="H1" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="K1" s="8" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A2" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="9" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="C2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B3" s="6" t="s">
+      <c r="D2" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A3" s="15"/>
+      <c r="B3" s="9"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="9"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A4" s="15"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="K4" s="9" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A5" s="15"/>
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="K5" s="9" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A6" s="15"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="K6" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A7" s="15"/>
+      <c r="B7" s="9"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="K7" s="9" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A8" s="15"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="K8" s="9" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A9" s="15"/>
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="9"/>
+      <c r="I9" s="9"/>
+      <c r="J9" s="9"/>
+      <c r="K9" s="9" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A10" s="15"/>
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="H10" s="9"/>
+      <c r="I10" s="9"/>
+      <c r="J10" s="9"/>
+      <c r="K10" s="9" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A11" s="15"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="9"/>
+      <c r="I11" s="9"/>
+      <c r="J11" s="9"/>
+      <c r="K11" s="9" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A12" s="15"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="9"/>
+      <c r="I12" s="9"/>
+      <c r="J12" s="9"/>
+      <c r="K12" s="9" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A13" s="15"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="9"/>
+      <c r="I13" s="9"/>
+      <c r="J13" s="9"/>
+      <c r="K13" s="9" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A14" s="15"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="9"/>
+      <c r="H14" s="9"/>
+      <c r="I14" s="9"/>
+      <c r="J14" s="9"/>
+      <c r="K14" s="9" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A15" s="15"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="9"/>
+      <c r="I15" s="9"/>
+      <c r="J15" s="9"/>
+      <c r="K15" s="9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A16" s="15"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="9"/>
+      <c r="I16" s="9"/>
+      <c r="J16" s="9"/>
+      <c r="K16" s="9" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A17" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="B17" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="C3" t="s">
-        <v>41</v>
+      <c r="C17" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="G17" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="H17" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="I17" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="J17" s="10"/>
+      <c r="K17" s="10" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A18" s="16"/>
+      <c r="B18" s="10"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="10"/>
+      <c r="F18" s="10"/>
+      <c r="G18" s="10"/>
+      <c r="H18" s="10"/>
+      <c r="I18" s="10"/>
+      <c r="J18" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="K18" s="10" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A19" s="16"/>
+      <c r="B19" s="10"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="10"/>
+      <c r="E19" s="10"/>
+      <c r="F19" s="10"/>
+      <c r="G19" s="10"/>
+      <c r="H19" s="10"/>
+      <c r="I19" s="10"/>
+      <c r="J19" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="K19" s="10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A20" s="16"/>
+      <c r="B20" s="10"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="10"/>
+      <c r="E20" s="10"/>
+      <c r="F20" s="10"/>
+      <c r="G20" s="10"/>
+      <c r="H20" s="10"/>
+      <c r="I20" s="10"/>
+      <c r="J20" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="K20" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A21" s="16"/>
+      <c r="B21" s="10"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="10"/>
+      <c r="F21" s="10"/>
+      <c r="G21" s="10"/>
+      <c r="H21" s="10"/>
+      <c r="I21" s="10"/>
+      <c r="J21" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="K21" s="10" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A22" s="16"/>
+      <c r="B22" s="10"/>
+      <c r="C22" s="10"/>
+      <c r="D22" s="10"/>
+      <c r="E22" s="10"/>
+      <c r="F22" s="10"/>
+      <c r="G22" s="10"/>
+      <c r="H22" s="10"/>
+      <c r="I22" s="10"/>
+      <c r="J22" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="K22" s="10" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A23" s="16"/>
+      <c r="B23" s="10"/>
+      <c r="C23" s="10"/>
+      <c r="D23" s="10"/>
+      <c r="E23" s="10"/>
+      <c r="F23" s="10"/>
+      <c r="G23" s="10"/>
+      <c r="H23" s="10"/>
+      <c r="I23" s="10"/>
+      <c r="J23" s="10"/>
+      <c r="K23" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A24" s="16"/>
+      <c r="B24" s="10"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="10"/>
+      <c r="F24" s="10"/>
+      <c r="G24" s="10"/>
+      <c r="H24" s="10"/>
+      <c r="I24" s="10"/>
+      <c r="J24" s="10"/>
+      <c r="K24" s="10" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A25" s="16"/>
+      <c r="B25" s="10"/>
+      <c r="C25" s="10"/>
+      <c r="D25" s="10"/>
+      <c r="E25" s="10"/>
+      <c r="F25" s="10"/>
+      <c r="G25" s="10"/>
+      <c r="H25" s="10"/>
+      <c r="I25" s="10"/>
+      <c r="J25" s="10"/>
+      <c r="K25" s="10" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A26" s="16"/>
+      <c r="B26" s="10"/>
+      <c r="C26" s="10"/>
+      <c r="D26" s="10"/>
+      <c r="E26" s="10"/>
+      <c r="F26" s="10"/>
+      <c r="G26" s="10"/>
+      <c r="H26" s="10"/>
+      <c r="I26" s="10"/>
+      <c r="J26" s="10"/>
+      <c r="K26" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A27" s="16"/>
+      <c r="B27" s="10"/>
+      <c r="C27" s="10"/>
+      <c r="D27" s="10"/>
+      <c r="E27" s="10"/>
+      <c r="F27" s="10"/>
+      <c r="G27" s="10"/>
+      <c r="H27" s="10"/>
+      <c r="I27" s="10"/>
+      <c r="J27" s="10"/>
+      <c r="K27" s="10" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A28" s="16"/>
+      <c r="B28" s="10"/>
+      <c r="C28" s="10"/>
+      <c r="D28" s="10"/>
+      <c r="E28" s="10"/>
+      <c r="F28" s="10"/>
+      <c r="G28" s="10"/>
+      <c r="H28" s="10"/>
+      <c r="I28" s="10"/>
+      <c r="J28" s="10"/>
+      <c r="K28" s="10" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A29" s="16"/>
+      <c r="B29" s="10"/>
+      <c r="C29" s="10"/>
+      <c r="D29" s="10"/>
+      <c r="E29" s="10"/>
+      <c r="F29" s="10"/>
+      <c r="G29" s="10"/>
+      <c r="H29" s="10"/>
+      <c r="I29" s="10"/>
+      <c r="J29" s="10"/>
+      <c r="K29" s="10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A30" s="16"/>
+      <c r="B30" s="10"/>
+      <c r="C30" s="10"/>
+      <c r="D30" s="10"/>
+      <c r="E30" s="10"/>
+      <c r="F30" s="10"/>
+      <c r="G30" s="10"/>
+      <c r="H30" s="10"/>
+      <c r="I30" s="10"/>
+      <c r="J30" s="10"/>
+      <c r="K30" s="10" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A31" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="B31" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="C31" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D31" s="11"/>
+      <c r="E31" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="F31" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="G31" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="H31" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="I31" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="J31" s="11"/>
+      <c r="K31" s="11" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A32" s="17"/>
+      <c r="B32" s="11"/>
+      <c r="C32" s="11"/>
+      <c r="D32" s="11"/>
+      <c r="E32" s="11"/>
+      <c r="F32" s="11"/>
+      <c r="G32" s="11"/>
+      <c r="H32" s="11"/>
+      <c r="I32" s="11"/>
+      <c r="J32" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="K32" s="11" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A33" s="17"/>
+      <c r="B33" s="11"/>
+      <c r="C33" s="11"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="11"/>
+      <c r="F33" s="11"/>
+      <c r="G33" s="11"/>
+      <c r="H33" s="11"/>
+      <c r="I33" s="11"/>
+      <c r="J33" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="K33" s="11" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A34" s="17"/>
+      <c r="B34" s="11"/>
+      <c r="C34" s="11"/>
+      <c r="D34" s="11"/>
+      <c r="E34" s="11"/>
+      <c r="F34" s="11"/>
+      <c r="G34" s="11"/>
+      <c r="H34" s="11"/>
+      <c r="I34" s="11"/>
+      <c r="J34" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="K34" s="11" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A35" s="17"/>
+      <c r="B35" s="11"/>
+      <c r="C35" s="11"/>
+      <c r="D35" s="11"/>
+      <c r="E35" s="11"/>
+      <c r="F35" s="11"/>
+      <c r="G35" s="11"/>
+      <c r="H35" s="11"/>
+      <c r="I35" s="11"/>
+      <c r="J35" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="K35" s="11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A36" s="17"/>
+      <c r="B36" s="11"/>
+      <c r="C36" s="11"/>
+      <c r="D36" s="11"/>
+      <c r="E36" s="11"/>
+      <c r="F36" s="11"/>
+      <c r="G36" s="11"/>
+      <c r="H36" s="11"/>
+      <c r="I36" s="11"/>
+      <c r="J36" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="K36" s="11" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A37" s="17"/>
+      <c r="B37" s="11"/>
+      <c r="C37" s="11"/>
+      <c r="D37" s="11"/>
+      <c r="E37" s="11"/>
+      <c r="F37" s="11"/>
+      <c r="G37" s="11"/>
+      <c r="H37" s="11"/>
+      <c r="I37" s="11"/>
+      <c r="J37" s="11"/>
+      <c r="K37" s="11" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A38" s="17"/>
+      <c r="B38" s="11"/>
+      <c r="C38" s="11"/>
+      <c r="D38" s="11"/>
+      <c r="E38" s="11"/>
+      <c r="F38" s="11"/>
+      <c r="G38" s="11"/>
+      <c r="H38" s="11"/>
+      <c r="I38" s="11"/>
+      <c r="J38" s="11"/>
+      <c r="K38" s="11" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A39" s="17"/>
+      <c r="B39" s="11"/>
+      <c r="C39" s="11"/>
+      <c r="D39" s="11"/>
+      <c r="E39" s="11"/>
+      <c r="F39" s="11"/>
+      <c r="G39" s="11"/>
+      <c r="H39" s="11"/>
+      <c r="I39" s="11"/>
+      <c r="J39" s="11"/>
+      <c r="K39" s="11" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A40" s="17"/>
+      <c r="B40" s="11"/>
+      <c r="C40" s="11"/>
+      <c r="D40" s="11"/>
+      <c r="E40" s="11"/>
+      <c r="F40" s="11"/>
+      <c r="G40" s="11"/>
+      <c r="H40" s="11"/>
+      <c r="I40" s="11"/>
+      <c r="J40" s="11"/>
+      <c r="K40" s="11" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A41" s="17"/>
+      <c r="B41" s="11"/>
+      <c r="C41" s="11"/>
+      <c r="D41" s="11"/>
+      <c r="E41" s="11"/>
+      <c r="F41" s="11"/>
+      <c r="G41" s="11"/>
+      <c r="H41" s="11"/>
+      <c r="I41" s="11"/>
+      <c r="J41" s="11"/>
+      <c r="K41" s="11" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A42" s="17"/>
+      <c r="B42" s="11"/>
+      <c r="C42" s="11"/>
+      <c r="D42" s="11"/>
+      <c r="E42" s="11"/>
+      <c r="F42" s="11"/>
+      <c r="G42" s="11"/>
+      <c r="H42" s="11"/>
+      <c r="I42" s="11"/>
+      <c r="J42" s="11"/>
+      <c r="K42" s="11" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A43" s="17"/>
+      <c r="B43" s="11"/>
+      <c r="C43" s="11"/>
+      <c r="D43" s="11"/>
+      <c r="E43" s="11"/>
+      <c r="F43" s="11"/>
+      <c r="G43" s="11"/>
+      <c r="H43" s="11"/>
+      <c r="I43" s="11"/>
+      <c r="J43" s="11"/>
+      <c r="K43" s="11" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A44" s="17"/>
+      <c r="B44" s="11"/>
+      <c r="C44" s="11"/>
+      <c r="D44" s="11"/>
+      <c r="E44" s="11"/>
+      <c r="F44" s="11"/>
+      <c r="G44" s="11"/>
+      <c r="H44" s="11"/>
+      <c r="I44" s="11"/>
+      <c r="J44" s="11"/>
+      <c r="K44" s="11" t="s">
+        <v>71</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B2" r:id="rId1" xr:uid="{63684EDB-5B25-C445-BBB2-0B76AF7CBFE1}"/>
-    <hyperlink ref="B3" r:id="rId2" xr:uid="{A7263C5D-69B9-0743-A243-8F017832656C}"/>
+    <hyperlink ref="B17" r:id="rId2" xr:uid="{A7263C5D-69B9-0743-A243-8F017832656C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>